--- a/Data/EXCEL/Transfer/salemon/20240711/8049-salemon-20240711.xlsx
+++ b/Data/EXCEL/Transfer/salemon/20240711/8049-salemon-20240711.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlsx\20240711\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\GithubProjects\GoodinfoData2DB\Data\EXCEL\Transfer\salemon\20240711\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{00DF65D2-0C25-413D-B9EF-E3A3040695DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8CF72ECF-4BE3-4A18-9100-E7C1750F4C03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="290" windowWidth="18240" windowHeight="13390" xr2:uid="{37EF9E26-BB99-44FF-A247-5595F3418D4E}"/>
+    <workbookView xWindow="768" yWindow="684" windowWidth="20004" windowHeight="13956" xr2:uid="{CFBBB314-486E-42A0-9925-24C7C261BDEB}"/>
   </bookViews>
   <sheets>
     <sheet name="8049-salemon-20240711" sheetId="2" r:id="rId1"/>
@@ -1261,20 +1261,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07DCB715-F496-4B02-BD20-BDE4F71CEEC7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{240198C7-2854-4450-8DE7-A4482FF62B89}">
   <dimension ref="A1:Q498"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="5.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="14" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.08984375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.36328125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="14" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -1301,7 +1301,7 @@
       <c r="P1" s="19"/>
       <c r="Q1" s="20"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="16"/>
       <c r="B2" s="15" t="s">
         <v>4</v>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="16"/>
       <c r="B3" s="16"/>
       <c r="C3" s="16"/>
@@ -1383,7 +1383,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="17"/>
       <c r="B4" s="17"/>
       <c r="C4" s="17"/>
@@ -1422,7 +1422,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>45444</v>
       </c>
@@ -1475,7 +1475,7 @@
         <v>-44.3</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="9">
         <v>45413</v>
       </c>
@@ -1528,7 +1528,7 @@
         <v>-43</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>45383</v>
       </c>
@@ -1581,7 +1581,7 @@
         <v>-39.6</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="9">
         <v>45352</v>
       </c>
@@ -1634,7 +1634,7 @@
         <v>-39.799999999999997</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>45323</v>
       </c>
@@ -1687,7 +1687,7 @@
         <v>-32.299999999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
         <v>45292</v>
       </c>
@@ -1740,7 +1740,7 @@
         <v>-5.29</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>45261</v>
       </c>
@@ -1793,7 +1793,7 @@
         <v>-13.8</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
         <v>45231</v>
       </c>
@@ -1846,7 +1846,7 @@
         <v>-8.76</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>45200</v>
       </c>
@@ -1899,7 +1899,7 @@
         <v>-5.45</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="9">
         <v>45170</v>
       </c>
@@ -1952,7 +1952,7 @@
         <v>-3.87</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>45139</v>
       </c>
@@ -2005,7 +2005,7 @@
         <v>-3.56</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="9">
         <v>45108</v>
       </c>
@@ -2058,7 +2058,7 @@
         <v>1.79</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>45078</v>
       </c>
@@ -2111,7 +2111,7 @@
         <v>6.78</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="9">
         <v>45047</v>
       </c>
@@ -2164,7 +2164,7 @@
         <v>15.1</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>45017</v>
       </c>
@@ -2217,7 +2217,7 @@
         <v>15.4</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="9">
         <v>44986</v>
       </c>
@@ -2270,7 +2270,7 @@
         <v>23.7</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>44958</v>
       </c>
@@ -2323,7 +2323,7 @@
         <v>28.2</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="9">
         <v>44927</v>
       </c>
@@ -2376,7 +2376,7 @@
         <v>-9.0399999999999991</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>44896</v>
       </c>
@@ -2429,7 +2429,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="9">
         <v>44866</v>
       </c>
@@ -2482,7 +2482,7 @@
         <v>17.7</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>44835</v>
       </c>
@@ -2535,7 +2535,7 @@
         <v>15.6</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="9">
         <v>44805</v>
       </c>
@@ -2588,7 +2588,7 @@
         <v>16.3</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>44774</v>
       </c>
@@ -2641,7 +2641,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="9">
         <v>44743</v>
       </c>
@@ -2694,7 +2694,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>44713</v>
       </c>
@@ -2747,7 +2747,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="9">
         <v>44682</v>
       </c>
@@ -2800,7 +2800,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>44652</v>
       </c>
@@ -2853,7 +2853,7 @@
         <v>10.199999999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="9">
         <v>44621</v>
       </c>
@@ -2906,7 +2906,7 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>44593</v>
       </c>
@@ -2959,7 +2959,7 @@
         <v>5.67</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="9">
         <v>44562</v>
       </c>
@@ -3012,7 +3012,7 @@
         <v>0.69</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>44531</v>
       </c>
@@ -3065,7 +3065,7 @@
         <v>14.1</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="9">
         <v>44501</v>
       </c>
@@ -3118,7 +3118,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>44470</v>
       </c>
@@ -3171,7 +3171,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="9">
         <v>44440</v>
       </c>
@@ -3224,7 +3224,7 @@
         <v>7.83</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>44409</v>
       </c>
@@ -3277,7 +3277,7 @@
         <v>7.58</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="9">
         <v>44378</v>
       </c>
@@ -3330,7 +3330,7 @@
         <v>4.6900000000000004</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>44348</v>
       </c>
@@ -3383,7 +3383,7 @@
         <v>-0.75</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="9">
         <v>44317</v>
       </c>
@@ -3436,7 +3436,7 @@
         <v>-1.71</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>44287</v>
       </c>
@@ -3489,7 +3489,7 @@
         <v>-0.63</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" s="9">
         <v>44256</v>
       </c>
@@ -3542,7 +3542,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
         <v>44228</v>
       </c>
@@ -3595,7 +3595,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="9">
         <v>44197</v>
       </c>
@@ -3648,7 +3648,7 @@
         <v>54.7</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="5">
         <v>44166</v>
       </c>
@@ -3701,7 +3701,7 @@
         <v>-7.14</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="9">
         <v>44136</v>
       </c>
@@ -3754,7 +3754,7 @@
         <v>-8.36</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" s="5">
         <v>44105</v>
       </c>
@@ -3807,7 +3807,7 @@
         <v>-8.41</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" s="9">
         <v>44075</v>
       </c>
@@ -3860,7 +3860,7 @@
         <v>-7.22</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" s="5">
         <v>44044</v>
       </c>
@@ -3913,7 +3913,7 @@
         <v>-6.14</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" s="9">
         <v>44013</v>
       </c>
@@ -3966,7 +3966,7 @@
         <v>-5.55</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" s="5">
         <v>43983</v>
       </c>
@@ -4019,7 +4019,7 @@
         <v>-4.51</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" s="9">
         <v>43952</v>
       </c>
@@ -4072,7 +4072,7 @@
         <v>-7.32</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" s="5">
         <v>43922</v>
       </c>
@@ -4125,7 +4125,7 @@
         <v>-7.6</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" s="9">
         <v>43891</v>
       </c>
@@ -4178,7 +4178,7 @@
         <v>-24</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" s="5">
         <v>43862</v>
       </c>
@@ -4231,7 +4231,7 @@
         <v>-24.6</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" s="9">
         <v>43831</v>
       </c>
@@ -4284,7 +4284,7 @@
         <v>-42.6</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" s="5">
         <v>43800</v>
       </c>
@@ -4337,7 +4337,7 @@
         <v>-1.75</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" s="9">
         <v>43770</v>
       </c>
@@ -4390,7 +4390,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" s="5">
         <v>43739</v>
       </c>
@@ -4443,7 +4443,7 @@
         <v>1.21</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" s="9">
         <v>43709</v>
       </c>
@@ -4496,7 +4496,7 @@
         <v>3.71</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" s="5">
         <v>43678</v>
       </c>
@@ -4549,7 +4549,7 @@
         <v>6.35</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" s="9">
         <v>43647</v>
       </c>
@@ -4602,7 +4602,7 @@
         <v>11.2</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" s="5">
         <v>43617</v>
       </c>
@@ -4655,7 +4655,7 @@
         <v>12.8</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" s="9">
         <v>43586</v>
       </c>
@@ -4708,7 +4708,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" s="5">
         <v>43556</v>
       </c>
@@ -4761,7 +4761,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" s="9">
         <v>43525</v>
       </c>
@@ -4814,7 +4814,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" s="5">
         <v>43497</v>
       </c>
@@ -4867,7 +4867,7 @@
         <v>31.2</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" s="9">
         <v>43466</v>
       </c>
@@ -4920,7 +4920,7 @@
         <v>35.200000000000003</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" s="5">
         <v>43435</v>
       </c>
@@ -4973,7 +4973,7 @@
         <v>9.02</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" s="9">
         <v>43405</v>
       </c>
@@ -5026,7 +5026,7 @@
         <v>7.67</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" s="5">
         <v>43374</v>
       </c>
@@ -5079,7 +5079,7 @@
         <v>7.27</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" s="9">
         <v>43344</v>
       </c>
@@ -5132,7 +5132,7 @@
         <v>5.26</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" s="5">
         <v>43313</v>
       </c>
@@ -5185,7 +5185,7 @@
         <v>2.79</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" s="9">
         <v>43282</v>
       </c>
@@ -5238,7 +5238,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" s="5">
         <v>43252</v>
       </c>
@@ -5291,7 +5291,7 @@
         <v>-1.41</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" s="9">
         <v>43221</v>
       </c>
@@ -5344,7 +5344,7 @@
         <v>-1.06</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" s="5">
         <v>43191</v>
       </c>
@@ -5397,7 +5397,7 @@
         <v>-1.69</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" s="9">
         <v>43160</v>
       </c>
@@ -5450,7 +5450,7 @@
         <v>-7.46</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" s="5">
         <v>43132</v>
       </c>
@@ -5503,7 +5503,7 @@
         <v>-13.5</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" s="9">
         <v>43101</v>
       </c>
@@ -5556,7 +5556,7 @@
         <v>-2.4700000000000002</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" s="5">
         <v>43070</v>
       </c>
@@ -5609,7 +5609,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" s="9">
         <v>43040</v>
       </c>
@@ -5662,7 +5662,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" s="5">
         <v>43009</v>
       </c>
@@ -5715,7 +5715,7 @@
         <v>14.6</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" s="9">
         <v>42979</v>
       </c>
@@ -5768,7 +5768,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" s="5">
         <v>42948</v>
       </c>
@@ -5821,7 +5821,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" s="9">
         <v>42917</v>
       </c>
@@ -5874,7 +5874,7 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" s="5">
         <v>42887</v>
       </c>
@@ -5927,7 +5927,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" s="9">
         <v>42856</v>
       </c>
@@ -5980,7 +5980,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" s="5">
         <v>42826</v>
       </c>
@@ -6033,7 +6033,7 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" s="9">
         <v>42795</v>
       </c>
@@ -6086,7 +6086,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" s="5">
         <v>42767</v>
       </c>
@@ -6139,7 +6139,7 @@
         <v>17.3</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" s="9">
         <v>42736</v>
       </c>
@@ -6192,7 +6192,7 @@
         <v>-2.38</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" s="5">
         <v>42705</v>
       </c>
@@ -6245,7 +6245,7 @@
         <v>5.12</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" s="9">
         <v>42675</v>
       </c>
@@ -6298,7 +6298,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A97" s="5">
         <v>42644</v>
       </c>
@@ -6351,7 +6351,7 @@
         <v>4.97</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A98" s="9">
         <v>42614</v>
       </c>
@@ -6404,7 +6404,7 @@
         <v>5.13</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A99" s="5">
         <v>42583</v>
       </c>
@@ -6457,7 +6457,7 @@
         <v>7.62</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A100" s="9">
         <v>42552</v>
       </c>
@@ -6510,7 +6510,7 @@
         <v>11.9</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A101" s="5">
         <v>42522</v>
       </c>
@@ -6563,7 +6563,7 @@
         <v>15.4</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A102" s="9">
         <v>42491</v>
       </c>
@@ -6616,7 +6616,7 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A103" s="5">
         <v>42461</v>
       </c>
@@ -6669,7 +6669,7 @@
         <v>9.9</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A104" s="9">
         <v>42430</v>
       </c>
@@ -6722,7 +6722,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A105" s="5">
         <v>42401</v>
       </c>
@@ -6775,7 +6775,7 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A106" s="9">
         <v>42370</v>
       </c>
@@ -6828,7 +6828,7 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A107" s="5">
         <v>42339</v>
       </c>
@@ -6881,7 +6881,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A108" s="9">
         <v>42309</v>
       </c>
@@ -6934,7 +6934,7 @@
         <v>11.9</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A109" s="5">
         <v>42278</v>
       </c>
@@ -6987,7 +6987,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A110" s="9">
         <v>42248</v>
       </c>
@@ -7040,7 +7040,7 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A111" s="5">
         <v>42217</v>
       </c>
@@ -7093,7 +7093,7 @@
         <v>7.53</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A112" s="9">
         <v>42186</v>
       </c>
@@ -7146,7 +7146,7 @@
         <v>5.96</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A113" s="5">
         <v>42156</v>
       </c>
@@ -7199,7 +7199,7 @@
         <v>-0.04</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A114" s="9">
         <v>42125</v>
       </c>
@@ -7252,7 +7252,7 @@
         <v>-0.01</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A115" s="5">
         <v>42095</v>
       </c>
@@ -7305,7 +7305,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A116" s="9">
         <v>42064</v>
       </c>
@@ -7358,7 +7358,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A117" s="5">
         <v>42036</v>
       </c>
@@ -7411,7 +7411,7 @@
         <v>5.98</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A118" s="9">
         <v>42005</v>
       </c>
@@ -7464,7 +7464,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A119" s="5">
         <v>41974</v>
       </c>
@@ -7517,7 +7517,7 @@
         <v>-3.23</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A120" s="9">
         <v>41944</v>
       </c>
@@ -7570,7 +7570,7 @@
         <v>-4.34</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A121" s="5">
         <v>41913</v>
       </c>
@@ -7623,7 +7623,7 @@
         <v>-4.5</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A122" s="9">
         <v>41883</v>
       </c>
@@ -7676,7 +7676,7 @@
         <v>-5.68</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A123" s="5">
         <v>41852</v>
       </c>
@@ -7729,7 +7729,7 @@
         <v>-4.03</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A124" s="9">
         <v>41821</v>
       </c>
@@ -7782,7 +7782,7 @@
         <v>-4.3499999999999996</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A125" s="5">
         <v>41791</v>
       </c>
@@ -7835,7 +7835,7 @@
         <v>-0.11</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A126" s="9">
         <v>41760</v>
       </c>
@@ -7888,7 +7888,7 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A127" s="5">
         <v>41730</v>
       </c>
@@ -7941,7 +7941,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A128" s="9">
         <v>41699</v>
       </c>
@@ -7994,7 +7994,7 @@
         <v>9.52</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A129" s="5">
         <v>41671</v>
       </c>
@@ -8047,7 +8047,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A130" s="9">
         <v>41640</v>
       </c>
@@ -8100,7 +8100,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A131" s="5">
         <v>41609</v>
       </c>
@@ -8153,7 +8153,7 @@
         <v>13.3</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A132" s="9">
         <v>41579</v>
       </c>
@@ -8206,7 +8206,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A133" s="5">
         <v>41548</v>
       </c>
@@ -8259,7 +8259,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A134" s="9">
         <v>41518</v>
       </c>
@@ -8312,7 +8312,7 @@
         <v>17.100000000000001</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A135" s="5">
         <v>41487</v>
       </c>
@@ -8365,7 +8365,7 @@
         <v>17.2</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A136" s="9">
         <v>41456</v>
       </c>
@@ -8418,7 +8418,7 @@
         <v>19.399999999999999</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A137" s="5">
         <v>41426</v>
       </c>
@@ -8471,7 +8471,7 @@
         <v>18.7</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A138" s="9">
         <v>41395</v>
       </c>
@@ -8524,7 +8524,7 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A139" s="5">
         <v>41365</v>
       </c>
@@ -8577,7 +8577,7 @@
         <v>8.94</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A140" s="9">
         <v>41334</v>
       </c>
@@ -8630,7 +8630,7 @@
         <v>8.89</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A141" s="5">
         <v>41306</v>
       </c>
@@ -8683,7 +8683,7 @@
         <v>-4.37</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A142" s="9">
         <v>41275</v>
       </c>
@@ -8736,7 +8736,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A143" s="5">
         <v>41244</v>
       </c>
@@ -8789,7 +8789,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A144" s="9">
         <v>41214</v>
       </c>
@@ -8842,7 +8842,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A145" s="5">
         <v>41183</v>
       </c>
@@ -8895,7 +8895,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A146" s="9">
         <v>41153</v>
       </c>
@@ -8948,7 +8948,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A147" s="5">
         <v>41122</v>
       </c>
@@ -9001,7 +9001,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A148" s="9">
         <v>41091</v>
       </c>
@@ -9054,7 +9054,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A149" s="5">
         <v>41061</v>
       </c>
@@ -9107,7 +9107,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A150" s="9">
         <v>41030</v>
       </c>
@@ -9160,7 +9160,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A151" s="5">
         <v>41000</v>
       </c>
@@ -9213,7 +9213,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A152" s="9">
         <v>40969</v>
       </c>
@@ -9266,7 +9266,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A153" s="5">
         <v>40940</v>
       </c>
@@ -9319,7 +9319,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A154" s="9">
         <v>40909</v>
       </c>
@@ -9372,7 +9372,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A155" s="5">
         <v>40878</v>
       </c>
@@ -9425,7 +9425,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A156" s="9">
         <v>40848</v>
       </c>
@@ -9478,7 +9478,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A157" s="5">
         <v>40817</v>
       </c>
@@ -9531,7 +9531,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A158" s="9">
         <v>40787</v>
       </c>
@@ -9584,7 +9584,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A159" s="5">
         <v>40756</v>
       </c>
@@ -9637,7 +9637,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A160" s="9">
         <v>40725</v>
       </c>
@@ -9690,7 +9690,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A161" s="5">
         <v>40695</v>
       </c>
@@ -9743,7 +9743,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A162" s="9">
         <v>40664</v>
       </c>
@@ -9796,7 +9796,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A163" s="5">
         <v>40634</v>
       </c>
@@ -9849,7 +9849,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A164" s="9">
         <v>40603</v>
       </c>
@@ -9902,7 +9902,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A165" s="5">
         <v>40575</v>
       </c>
@@ -9955,7 +9955,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A166" s="9">
         <v>40544</v>
       </c>
@@ -10008,7 +10008,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A167" s="5">
         <v>40513</v>
       </c>
@@ -10061,7 +10061,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A168" s="9">
         <v>40483</v>
       </c>
@@ -10114,7 +10114,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A169" s="5">
         <v>40452</v>
       </c>
@@ -10167,7 +10167,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A170" s="9">
         <v>40422</v>
       </c>
@@ -10220,7 +10220,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A171" s="5">
         <v>40391</v>
       </c>
@@ -10273,7 +10273,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A172" s="9">
         <v>40360</v>
       </c>
@@ -10326,7 +10326,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A173" s="5">
         <v>40330</v>
       </c>
@@ -10379,7 +10379,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A174" s="9">
         <v>40299</v>
       </c>
@@ -10432,7 +10432,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A175" s="5">
         <v>40269</v>
       </c>
@@ -10485,7 +10485,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A176" s="9">
         <v>40238</v>
       </c>
@@ -10538,7 +10538,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A177" s="5">
         <v>40210</v>
       </c>
@@ -10591,7 +10591,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="178" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A178" s="9">
         <v>40179</v>
       </c>
@@ -10644,7 +10644,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A179" s="5">
         <v>40148</v>
       </c>
@@ -10697,7 +10697,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A180" s="9">
         <v>40118</v>
       </c>
@@ -10750,7 +10750,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A181" s="5">
         <v>40087</v>
       </c>
@@ -10803,7 +10803,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A182" s="9">
         <v>40057</v>
       </c>
@@ -10856,7 +10856,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A183" s="5">
         <v>40026</v>
       </c>
@@ -10909,7 +10909,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A184" s="9">
         <v>39995</v>
       </c>
@@ -10962,7 +10962,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A185" s="5">
         <v>39965</v>
       </c>
@@ -11015,7 +11015,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A186" s="9">
         <v>39934</v>
       </c>
@@ -11068,7 +11068,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="187" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A187" s="5">
         <v>39904</v>
       </c>
@@ -11121,7 +11121,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="188" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A188" s="9">
         <v>39873</v>
       </c>
@@ -11174,7 +11174,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="189" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A189" s="5">
         <v>39845</v>
       </c>
@@ -11227,7 +11227,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="190" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A190" s="9">
         <v>39814</v>
       </c>
@@ -11280,7 +11280,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="191" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A191" s="5">
         <v>39783</v>
       </c>
@@ -11333,7 +11333,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="192" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A192" s="9">
         <v>39753</v>
       </c>
@@ -11386,7 +11386,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="193" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A193" s="5">
         <v>39722</v>
       </c>
@@ -11439,7 +11439,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="194" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A194" s="9">
         <v>39692</v>
       </c>
@@ -11492,7 +11492,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="195" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A195" s="5">
         <v>39661</v>
       </c>
@@ -11545,7 +11545,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="196" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A196" s="9">
         <v>39630</v>
       </c>
@@ -11598,7 +11598,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="197" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A197" s="5">
         <v>39600</v>
       </c>
@@ -11651,7 +11651,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="198" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A198" s="9">
         <v>39569</v>
       </c>
@@ -11704,7 +11704,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="199" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A199" s="5">
         <v>39539</v>
       </c>
@@ -11757,7 +11757,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="200" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A200" s="9">
         <v>39508</v>
       </c>
@@ -11810,7 +11810,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="201" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A201" s="5">
         <v>39479</v>
       </c>
@@ -11863,7 +11863,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="202" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A202" s="9">
         <v>39448</v>
       </c>
@@ -11916,7 +11916,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="203" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A203" s="5">
         <v>39417</v>
       </c>
@@ -11969,7 +11969,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="204" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A204" s="9">
         <v>39387</v>
       </c>
@@ -12022,7 +12022,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="205" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A205" s="5">
         <v>39356</v>
       </c>
@@ -12075,7 +12075,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="206" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A206" s="9">
         <v>39326</v>
       </c>
@@ -12128,7 +12128,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="207" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A207" s="5">
         <v>39295</v>
       </c>
@@ -12181,7 +12181,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="208" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A208" s="9">
         <v>39264</v>
       </c>
@@ -12234,7 +12234,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="209" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A209" s="5">
         <v>39234</v>
       </c>
@@ -12287,7 +12287,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="210" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A210" s="9">
         <v>39203</v>
       </c>
@@ -12340,7 +12340,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="211" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A211" s="5">
         <v>39173</v>
       </c>
@@ -12393,7 +12393,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="212" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A212" s="9">
         <v>39142</v>
       </c>
@@ -12446,7 +12446,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="213" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A213" s="5">
         <v>39114</v>
       </c>
@@ -12499,7 +12499,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="214" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A214" s="9">
         <v>39083</v>
       </c>
@@ -12552,7 +12552,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="215" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A215" s="5">
         <v>39052</v>
       </c>
@@ -12605,7 +12605,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="216" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A216" s="9">
         <v>39022</v>
       </c>
@@ -12658,7 +12658,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="217" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A217" s="5">
         <v>38991</v>
       </c>
@@ -12711,7 +12711,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="218" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A218" s="9">
         <v>38961</v>
       </c>
@@ -12764,7 +12764,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="219" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A219" s="5">
         <v>38930</v>
       </c>
@@ -12817,7 +12817,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="220" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A220" s="9">
         <v>38899</v>
       </c>
@@ -12870,7 +12870,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="221" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A221" s="5">
         <v>38869</v>
       </c>
@@ -12923,7 +12923,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="222" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A222" s="9">
         <v>38838</v>
       </c>
@@ -12976,7 +12976,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="223" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A223" s="5">
         <v>38808</v>
       </c>
@@ -13029,7 +13029,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="224" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A224" s="9">
         <v>38777</v>
       </c>
@@ -13082,7 +13082,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="225" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A225" s="5">
         <v>38749</v>
       </c>
@@ -13135,7 +13135,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="226" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A226" s="9">
         <v>38718</v>
       </c>
@@ -13188,7 +13188,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="227" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A227" s="5">
         <v>38687</v>
       </c>
@@ -13241,7 +13241,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="228" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A228" s="9">
         <v>38657</v>
       </c>
@@ -13294,7 +13294,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="229" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A229" s="5">
         <v>38626</v>
       </c>
@@ -13347,7 +13347,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="230" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A230" s="9">
         <v>38596</v>
       </c>
@@ -13400,7 +13400,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="231" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A231" s="5">
         <v>38565</v>
       </c>
@@ -13453,7 +13453,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="232" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A232" s="9">
         <v>38534</v>
       </c>
@@ -13506,7 +13506,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="233" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A233" s="5">
         <v>38504</v>
       </c>
@@ -13559,7 +13559,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="234" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A234" s="9">
         <v>38473</v>
       </c>
@@ -13612,7 +13612,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="235" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A235" s="5">
         <v>38443</v>
       </c>
@@ -13665,7 +13665,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="236" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A236" s="9">
         <v>38412</v>
       </c>
@@ -13718,7 +13718,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="237" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A237" s="5">
         <v>38384</v>
       </c>
@@ -13771,7 +13771,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="238" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A238" s="9">
         <v>38353</v>
       </c>
@@ -13824,7 +13824,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="239" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A239" s="5">
         <v>38322</v>
       </c>
@@ -13877,7 +13877,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="240" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A240" s="9">
         <v>38292</v>
       </c>
@@ -13930,7 +13930,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="241" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="241" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A241" s="5">
         <v>38261</v>
       </c>
@@ -13983,7 +13983,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="242" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="242" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A242" s="9">
         <v>38231</v>
       </c>
@@ -14036,7 +14036,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="243" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="243" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A243" s="5">
         <v>38200</v>
       </c>
@@ -14089,7 +14089,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="244" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="244" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A244" s="9">
         <v>38169</v>
       </c>
@@ -14142,1272 +14142,1272 @@
         <v>17</v>
       </c>
     </row>
-    <row r="245" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="245" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A245" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A246" s="5">
         <v>45444</v>
       </c>
     </row>
-    <row r="247" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="247" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A247" s="9">
         <v>45413</v>
       </c>
     </row>
-    <row r="248" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="248" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A248" s="5">
         <v>45383</v>
       </c>
     </row>
-    <row r="249" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="249" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A249" s="9">
         <v>45352</v>
       </c>
     </row>
-    <row r="250" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="250" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A250" s="5">
         <v>45323</v>
       </c>
     </row>
-    <row r="251" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="251" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A251" s="9">
         <v>45292</v>
       </c>
     </row>
-    <row r="252" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="252" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A252" s="5">
         <v>45261</v>
       </c>
     </row>
-    <row r="253" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="253" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A253" s="9">
         <v>45231</v>
       </c>
     </row>
-    <row r="254" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="254" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A254" s="5">
         <v>45200</v>
       </c>
     </row>
-    <row r="255" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="255" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A255" s="9">
         <v>45170</v>
       </c>
     </row>
-    <row r="256" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="256" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A256" s="5">
         <v>45139</v>
       </c>
     </row>
-    <row r="257" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="257" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A257" s="9">
         <v>45108</v>
       </c>
     </row>
-    <row r="258" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="258" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A258" s="5">
         <v>45078</v>
       </c>
     </row>
-    <row r="259" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="259" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A259" s="9">
         <v>45047</v>
       </c>
     </row>
-    <row r="260" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="260" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A260" s="5">
         <v>45017</v>
       </c>
     </row>
-    <row r="261" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A261" s="9">
         <v>44986</v>
       </c>
     </row>
-    <row r="262" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="262" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A262" s="5">
         <v>44958</v>
       </c>
     </row>
-    <row r="263" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="263" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A263" s="9">
         <v>44927</v>
       </c>
     </row>
-    <row r="264" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="264" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A264" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="265" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A265" s="5">
         <v>44896</v>
       </c>
     </row>
-    <row r="266" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="266" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A266" s="9">
         <v>44866</v>
       </c>
     </row>
-    <row r="267" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="267" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A267" s="5">
         <v>44835</v>
       </c>
     </row>
-    <row r="268" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="268" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A268" s="9">
         <v>44805</v>
       </c>
     </row>
-    <row r="269" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="269" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A269" s="5">
         <v>44774</v>
       </c>
     </row>
-    <row r="270" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="270" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A270" s="9">
         <v>44743</v>
       </c>
     </row>
-    <row r="271" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="271" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A271" s="5">
         <v>44713</v>
       </c>
     </row>
-    <row r="272" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="272" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A272" s="9">
         <v>44682</v>
       </c>
     </row>
-    <row r="273" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="273" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A273" s="5">
         <v>44652</v>
       </c>
     </row>
-    <row r="274" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="274" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A274" s="9">
         <v>44621</v>
       </c>
     </row>
-    <row r="275" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="275" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A275" s="5">
         <v>44593</v>
       </c>
     </row>
-    <row r="276" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="276" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A276" s="9">
         <v>44562</v>
       </c>
     </row>
-    <row r="277" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="277" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A277" s="5">
         <v>44531</v>
       </c>
     </row>
-    <row r="278" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="278" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A278" s="9">
         <v>44501</v>
       </c>
     </row>
-    <row r="279" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="279" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A279" s="5">
         <v>44470</v>
       </c>
     </row>
-    <row r="280" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="280" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A280" s="9">
         <v>44440</v>
       </c>
     </row>
-    <row r="281" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="281" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A281" s="5">
         <v>44409</v>
       </c>
     </row>
-    <row r="282" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="282" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A282" s="9">
         <v>44378</v>
       </c>
     </row>
-    <row r="283" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="283" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A283" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="284" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A284" s="5">
         <v>44348</v>
       </c>
     </row>
-    <row r="285" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="285" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A285" s="9">
         <v>44317</v>
       </c>
     </row>
-    <row r="286" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="286" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A286" s="5">
         <v>44287</v>
       </c>
     </row>
-    <row r="287" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="287" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A287" s="9">
         <v>44256</v>
       </c>
     </row>
-    <row r="288" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="288" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A288" s="5">
         <v>44228</v>
       </c>
     </row>
-    <row r="289" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="289" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A289" s="9">
         <v>44197</v>
       </c>
     </row>
-    <row r="290" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="290" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A290" s="5">
         <v>44166</v>
       </c>
     </row>
-    <row r="291" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="291" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A291" s="9">
         <v>44136</v>
       </c>
     </row>
-    <row r="292" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="292" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A292" s="5">
         <v>44105</v>
       </c>
     </row>
-    <row r="293" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="293" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A293" s="9">
         <v>44075</v>
       </c>
     </row>
-    <row r="294" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="294" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A294" s="5">
         <v>44044</v>
       </c>
     </row>
-    <row r="295" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="295" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A295" s="9">
         <v>44013</v>
       </c>
     </row>
-    <row r="296" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="296" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A296" s="5">
         <v>43983</v>
       </c>
     </row>
-    <row r="297" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="297" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A297" s="9">
         <v>43952</v>
       </c>
     </row>
-    <row r="298" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="298" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A298" s="5">
         <v>43922</v>
       </c>
     </row>
-    <row r="299" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="299" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A299" s="9">
         <v>43891</v>
       </c>
     </row>
-    <row r="300" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="300" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A300" s="5">
         <v>43862</v>
       </c>
     </row>
-    <row r="301" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="301" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A301" s="9">
         <v>43831</v>
       </c>
     </row>
-    <row r="302" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="302" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A302" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="303" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A303" s="5">
         <v>43800</v>
       </c>
     </row>
-    <row r="304" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="304" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A304" s="9">
         <v>43770</v>
       </c>
     </row>
-    <row r="305" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="305" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A305" s="5">
         <v>43739</v>
       </c>
     </row>
-    <row r="306" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="306" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A306" s="9">
         <v>43709</v>
       </c>
     </row>
-    <row r="307" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="307" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A307" s="5">
         <v>43678</v>
       </c>
     </row>
-    <row r="308" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="308" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A308" s="9">
         <v>43647</v>
       </c>
     </row>
-    <row r="309" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="309" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A309" s="5">
         <v>43617</v>
       </c>
     </row>
-    <row r="310" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="310" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A310" s="9">
         <v>43586</v>
       </c>
     </row>
-    <row r="311" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="311" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A311" s="5">
         <v>43556</v>
       </c>
     </row>
-    <row r="312" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="312" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A312" s="9">
         <v>43525</v>
       </c>
     </row>
-    <row r="313" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="313" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A313" s="5">
         <v>43497</v>
       </c>
     </row>
-    <row r="314" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="314" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A314" s="9">
         <v>43466</v>
       </c>
     </row>
-    <row r="315" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="315" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A315" s="5">
         <v>43435</v>
       </c>
     </row>
-    <row r="316" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="316" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A316" s="9">
         <v>43405</v>
       </c>
     </row>
-    <row r="317" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="317" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A317" s="5">
         <v>43374</v>
       </c>
     </row>
-    <row r="318" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="318" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A318" s="9">
         <v>43344</v>
       </c>
     </row>
-    <row r="319" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="319" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A319" s="5">
         <v>43313</v>
       </c>
     </row>
-    <row r="320" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="320" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A320" s="9">
         <v>43282</v>
       </c>
     </row>
-    <row r="321" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="321" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A321" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="322" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A322" s="5">
         <v>43252</v>
       </c>
     </row>
-    <row r="323" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="323" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A323" s="9">
         <v>43221</v>
       </c>
     </row>
-    <row r="324" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="324" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A324" s="5">
         <v>43191</v>
       </c>
     </row>
-    <row r="325" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="325" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A325" s="9">
         <v>43160</v>
       </c>
     </row>
-    <row r="326" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="326" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A326" s="5">
         <v>43132</v>
       </c>
     </row>
-    <row r="327" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="327" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A327" s="9">
         <v>43101</v>
       </c>
     </row>
-    <row r="328" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="328" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A328" s="5">
         <v>43070</v>
       </c>
     </row>
-    <row r="329" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="329" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A329" s="9">
         <v>43040</v>
       </c>
     </row>
-    <row r="330" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="330" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A330" s="5">
         <v>43009</v>
       </c>
     </row>
-    <row r="331" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="331" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A331" s="9">
         <v>42979</v>
       </c>
     </row>
-    <row r="332" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="332" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A332" s="5">
         <v>42948</v>
       </c>
     </row>
-    <row r="333" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="333" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A333" s="9">
         <v>42917</v>
       </c>
     </row>
-    <row r="334" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="334" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A334" s="5">
         <v>42887</v>
       </c>
     </row>
-    <row r="335" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="335" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A335" s="9">
         <v>42856</v>
       </c>
     </row>
-    <row r="336" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="336" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A336" s="5">
         <v>42826</v>
       </c>
     </row>
-    <row r="337" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="337" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A337" s="9">
         <v>42795</v>
       </c>
     </row>
-    <row r="338" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="338" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A338" s="5">
         <v>42767</v>
       </c>
     </row>
-    <row r="339" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="339" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A339" s="9">
         <v>42736</v>
       </c>
     </row>
-    <row r="340" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="340" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A340" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="341" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A341" s="5">
         <v>42705</v>
       </c>
     </row>
-    <row r="342" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="342" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A342" s="9">
         <v>42675</v>
       </c>
     </row>
-    <row r="343" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="343" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A343" s="5">
         <v>42644</v>
       </c>
     </row>
-    <row r="344" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="344" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A344" s="9">
         <v>42614</v>
       </c>
     </row>
-    <row r="345" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="345" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A345" s="5">
         <v>42583</v>
       </c>
     </row>
-    <row r="346" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="346" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A346" s="9">
         <v>42552</v>
       </c>
     </row>
-    <row r="347" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="347" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A347" s="5">
         <v>42522</v>
       </c>
     </row>
-    <row r="348" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="348" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A348" s="9">
         <v>42491</v>
       </c>
     </row>
-    <row r="349" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="349" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A349" s="5">
         <v>42461</v>
       </c>
     </row>
-    <row r="350" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="350" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A350" s="9">
         <v>42430</v>
       </c>
     </row>
-    <row r="351" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="351" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A351" s="5">
         <v>42401</v>
       </c>
     </row>
-    <row r="352" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="352" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A352" s="9">
         <v>42370</v>
       </c>
     </row>
-    <row r="353" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="353" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A353" s="5">
         <v>42339</v>
       </c>
     </row>
-    <row r="354" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="354" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A354" s="9">
         <v>42309</v>
       </c>
     </row>
-    <row r="355" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="355" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A355" s="5">
         <v>42278</v>
       </c>
     </row>
-    <row r="356" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="356" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A356" s="9">
         <v>42248</v>
       </c>
     </row>
-    <row r="357" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="357" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A357" s="5">
         <v>42217</v>
       </c>
     </row>
-    <row r="358" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="358" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A358" s="9">
         <v>42186</v>
       </c>
     </row>
-    <row r="359" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="359" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A359" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="360" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="360" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A360" s="5">
         <v>42156</v>
       </c>
     </row>
-    <row r="361" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="361" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A361" s="9">
         <v>42125</v>
       </c>
     </row>
-    <row r="362" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="362" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A362" s="5">
         <v>42095</v>
       </c>
     </row>
-    <row r="363" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="363" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A363" s="9">
         <v>42064</v>
       </c>
     </row>
-    <row r="364" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="364" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A364" s="5">
         <v>42036</v>
       </c>
     </row>
-    <row r="365" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="365" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A365" s="9">
         <v>42005</v>
       </c>
     </row>
-    <row r="366" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="366" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A366" s="5">
         <v>41974</v>
       </c>
     </row>
-    <row r="367" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="367" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A367" s="9">
         <v>41944</v>
       </c>
     </row>
-    <row r="368" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="368" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A368" s="5">
         <v>41913</v>
       </c>
     </row>
-    <row r="369" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="369" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A369" s="9">
         <v>41883</v>
       </c>
     </row>
-    <row r="370" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="370" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A370" s="5">
         <v>41852</v>
       </c>
     </row>
-    <row r="371" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="371" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A371" s="9">
         <v>41821</v>
       </c>
     </row>
-    <row r="372" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="372" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A372" s="5">
         <v>41791</v>
       </c>
     </row>
-    <row r="373" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="373" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A373" s="9">
         <v>41760</v>
       </c>
     </row>
-    <row r="374" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="374" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A374" s="5">
         <v>41730</v>
       </c>
     </row>
-    <row r="375" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="375" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A375" s="9">
         <v>41699</v>
       </c>
     </row>
-    <row r="376" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="376" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A376" s="5">
         <v>41671</v>
       </c>
     </row>
-    <row r="377" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="377" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A377" s="9">
         <v>41640</v>
       </c>
     </row>
-    <row r="378" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="378" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A378" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="379" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="379" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A379" s="5">
         <v>41609</v>
       </c>
     </row>
-    <row r="380" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="380" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A380" s="9">
         <v>41579</v>
       </c>
     </row>
-    <row r="381" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="381" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A381" s="5">
         <v>41548</v>
       </c>
     </row>
-    <row r="382" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="382" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A382" s="9">
         <v>41518</v>
       </c>
     </row>
-    <row r="383" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="383" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A383" s="5">
         <v>41487</v>
       </c>
     </row>
-    <row r="384" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="384" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A384" s="9">
         <v>41456</v>
       </c>
     </row>
-    <row r="385" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="385" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A385" s="5">
         <v>41426</v>
       </c>
     </row>
-    <row r="386" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="386" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A386" s="9">
         <v>41395</v>
       </c>
     </row>
-    <row r="387" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="387" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A387" s="5">
         <v>41365</v>
       </c>
     </row>
-    <row r="388" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="388" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A388" s="9">
         <v>41334</v>
       </c>
     </row>
-    <row r="389" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="389" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A389" s="5">
         <v>41306</v>
       </c>
     </row>
-    <row r="390" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="390" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A390" s="9">
         <v>41275</v>
       </c>
     </row>
-    <row r="391" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="391" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A391" s="5">
         <v>41244</v>
       </c>
     </row>
-    <row r="392" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="392" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A392" s="9">
         <v>41214</v>
       </c>
     </row>
-    <row r="393" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="393" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A393" s="5">
         <v>41183</v>
       </c>
     </row>
-    <row r="394" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="394" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A394" s="9">
         <v>41153</v>
       </c>
     </row>
-    <row r="395" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="395" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A395" s="5">
         <v>41122</v>
       </c>
     </row>
-    <row r="396" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="396" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A396" s="9">
         <v>41091</v>
       </c>
     </row>
-    <row r="397" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="397" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A397" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="398" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="398" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A398" s="5">
         <v>41061</v>
       </c>
     </row>
-    <row r="399" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="399" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A399" s="9">
         <v>41030</v>
       </c>
     </row>
-    <row r="400" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="400" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A400" s="5">
         <v>41000</v>
       </c>
     </row>
-    <row r="401" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="401" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A401" s="9">
         <v>40969</v>
       </c>
     </row>
-    <row r="402" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="402" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A402" s="5">
         <v>40940</v>
       </c>
     </row>
-    <row r="403" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="403" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A403" s="9">
         <v>40909</v>
       </c>
     </row>
-    <row r="404" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="404" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A404" s="5">
         <v>40878</v>
       </c>
     </row>
-    <row r="405" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="405" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A405" s="9">
         <v>40848</v>
       </c>
     </row>
-    <row r="406" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="406" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A406" s="5">
         <v>40817</v>
       </c>
     </row>
-    <row r="407" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="407" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A407" s="9">
         <v>40787</v>
       </c>
     </row>
-    <row r="408" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="408" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A408" s="5">
         <v>40756</v>
       </c>
     </row>
-    <row r="409" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="409" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A409" s="9">
         <v>40725</v>
       </c>
     </row>
-    <row r="410" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="410" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A410" s="5">
         <v>40695</v>
       </c>
     </row>
-    <row r="411" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="411" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A411" s="9">
         <v>40664</v>
       </c>
     </row>
-    <row r="412" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="412" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A412" s="5">
         <v>40634</v>
       </c>
     </row>
-    <row r="413" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="413" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A413" s="9">
         <v>40603</v>
       </c>
     </row>
-    <row r="414" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="414" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A414" s="5">
         <v>40575</v>
       </c>
     </row>
-    <row r="415" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="415" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A415" s="9">
         <v>40544</v>
       </c>
     </row>
-    <row r="416" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="416" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A416" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="417" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="417" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A417" s="5">
         <v>40513</v>
       </c>
     </row>
-    <row r="418" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="418" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A418" s="9">
         <v>40483</v>
       </c>
     </row>
-    <row r="419" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="419" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A419" s="5">
         <v>40452</v>
       </c>
     </row>
-    <row r="420" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="420" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A420" s="9">
         <v>40422</v>
       </c>
     </row>
-    <row r="421" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="421" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A421" s="5">
         <v>40391</v>
       </c>
     </row>
-    <row r="422" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="422" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A422" s="9">
         <v>40360</v>
       </c>
     </row>
-    <row r="423" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="423" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A423" s="5">
         <v>40330</v>
       </c>
     </row>
-    <row r="424" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="424" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A424" s="9">
         <v>40299</v>
       </c>
     </row>
-    <row r="425" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="425" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A425" s="5">
         <v>40269</v>
       </c>
     </row>
-    <row r="426" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="426" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A426" s="9">
         <v>40238</v>
       </c>
     </row>
-    <row r="427" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="427" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A427" s="5">
         <v>40210</v>
       </c>
     </row>
-    <row r="428" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="428" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A428" s="9">
         <v>40179</v>
       </c>
     </row>
-    <row r="429" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="429" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A429" s="5">
         <v>40148</v>
       </c>
     </row>
-    <row r="430" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="430" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A430" s="9">
         <v>40118</v>
       </c>
     </row>
-    <row r="431" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="431" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A431" s="5">
         <v>40087</v>
       </c>
     </row>
-    <row r="432" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="432" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A432" s="9">
         <v>40057</v>
       </c>
     </row>
-    <row r="433" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="433" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A433" s="5">
         <v>40026</v>
       </c>
     </row>
-    <row r="434" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="434" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A434" s="9">
         <v>39995</v>
       </c>
     </row>
-    <row r="435" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="435" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A435" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="436" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="436" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A436" s="5">
         <v>39965</v>
       </c>
     </row>
-    <row r="437" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="437" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A437" s="9">
         <v>39934</v>
       </c>
     </row>
-    <row r="438" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="438" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A438" s="5">
         <v>39904</v>
       </c>
     </row>
-    <row r="439" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="439" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A439" s="9">
         <v>39873</v>
       </c>
     </row>
-    <row r="440" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="440" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A440" s="5">
         <v>39845</v>
       </c>
     </row>
-    <row r="441" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="441" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A441" s="9">
         <v>39814</v>
       </c>
     </row>
-    <row r="442" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="442" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A442" s="5">
         <v>39783</v>
       </c>
     </row>
-    <row r="443" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="443" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A443" s="9">
         <v>39753</v>
       </c>
     </row>
-    <row r="444" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="444" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A444" s="5">
         <v>39722</v>
       </c>
     </row>
-    <row r="445" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="445" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A445" s="9">
         <v>39692</v>
       </c>
     </row>
-    <row r="446" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="446" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A446" s="5">
         <v>39661</v>
       </c>
     </row>
-    <row r="447" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="447" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A447" s="9">
         <v>39630</v>
       </c>
     </row>
-    <row r="448" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="448" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A448" s="5">
         <v>39600</v>
       </c>
     </row>
-    <row r="449" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="449" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A449" s="9">
         <v>39569</v>
       </c>
     </row>
-    <row r="450" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="450" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A450" s="5">
         <v>39539</v>
       </c>
     </row>
-    <row r="451" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="451" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A451" s="9">
         <v>39508</v>
       </c>
     </row>
-    <row r="452" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="452" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A452" s="5">
         <v>39479</v>
       </c>
     </row>
-    <row r="453" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="453" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A453" s="9">
         <v>39448</v>
       </c>
     </row>
-    <row r="454" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="454" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A454" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="455" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="455" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A455" s="5">
         <v>39417</v>
       </c>
     </row>
-    <row r="456" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="456" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A456" s="9">
         <v>39387</v>
       </c>
     </row>
-    <row r="457" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="457" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A457" s="5">
         <v>39356</v>
       </c>
     </row>
-    <row r="458" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="458" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A458" s="9">
         <v>39326</v>
       </c>
     </row>
-    <row r="459" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="459" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A459" s="5">
         <v>39295</v>
       </c>
     </row>
-    <row r="460" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="460" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A460" s="9">
         <v>39264</v>
       </c>
     </row>
-    <row r="461" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="461" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A461" s="5">
         <v>39234</v>
       </c>
     </row>
-    <row r="462" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="462" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A462" s="9">
         <v>39203</v>
       </c>
     </row>
-    <row r="463" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="463" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A463" s="5">
         <v>39173</v>
       </c>
     </row>
-    <row r="464" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="464" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A464" s="9">
         <v>39142</v>
       </c>
     </row>
-    <row r="465" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="465" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A465" s="5">
         <v>39114</v>
       </c>
     </row>
-    <row r="466" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="466" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A466" s="9">
         <v>39083</v>
       </c>
     </row>
-    <row r="467" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="467" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A467" s="5">
         <v>39052</v>
       </c>
     </row>
-    <row r="468" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="468" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A468" s="9">
         <v>39022</v>
       </c>
     </row>
-    <row r="469" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="469" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A469" s="5">
         <v>38991</v>
       </c>
     </row>
-    <row r="470" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="470" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A470" s="9">
         <v>38961</v>
       </c>
     </row>
-    <row r="471" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="471" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A471" s="5">
         <v>38930</v>
       </c>
     </row>
-    <row r="472" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="472" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A472" s="9">
         <v>38899</v>
       </c>
     </row>
-    <row r="473" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="473" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A473" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="474" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="474" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A474" s="5">
         <v>38869</v>
       </c>
     </row>
-    <row r="475" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="475" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A475" s="9">
         <v>38838</v>
       </c>
     </row>
-    <row r="476" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="476" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A476" s="5">
         <v>38808</v>
       </c>
     </row>
-    <row r="477" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="477" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A477" s="9">
         <v>38777</v>
       </c>
     </row>
-    <row r="478" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="478" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A478" s="5">
         <v>38749</v>
       </c>
     </row>
-    <row r="479" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="479" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A479" s="9">
         <v>38718</v>
       </c>
     </row>
-    <row r="480" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="480" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A480" s="5">
         <v>38687</v>
       </c>
     </row>
-    <row r="481" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="481" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A481" s="9">
         <v>38657</v>
       </c>
     </row>
-    <row r="482" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="482" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A482" s="5">
         <v>38626</v>
       </c>
     </row>
-    <row r="483" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="483" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A483" s="9">
         <v>38596</v>
       </c>
     </row>
-    <row r="484" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="484" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A484" s="5">
         <v>38565</v>
       </c>
     </row>
-    <row r="485" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="485" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A485" s="9">
         <v>38534</v>
       </c>
     </row>
-    <row r="486" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="486" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A486" s="5">
         <v>38504</v>
       </c>
     </row>
-    <row r="487" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="487" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A487" s="9">
         <v>38473</v>
       </c>
     </row>
-    <row r="488" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="488" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A488" s="5">
         <v>38443</v>
       </c>
     </row>
-    <row r="489" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="489" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A489" s="9">
         <v>38412</v>
       </c>
     </row>
-    <row r="490" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="490" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A490" s="5">
         <v>38384</v>
       </c>
     </row>
-    <row r="491" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="491" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A491" s="9">
         <v>38353</v>
       </c>
     </row>
-    <row r="492" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="492" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A492" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="493" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="493" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A493" s="5">
         <v>38322</v>
       </c>
     </row>
-    <row r="494" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="494" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A494" s="9">
         <v>38292</v>
       </c>
     </row>
-    <row r="495" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="495" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A495" s="5">
         <v>38261</v>
       </c>
     </row>
-    <row r="496" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="496" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A496" s="9">
         <v>38231</v>
       </c>
     </row>
-    <row r="497" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="497" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A497" s="5">
         <v>38200</v>
       </c>
     </row>
-    <row r="498" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="498" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A498" s="9">
         <v>38169</v>
       </c>
